--- a/api/1/xlsx/pt/SectorGroup.xlsx
+++ b/api/1/xlsx/pt/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>Educação, nível não especificado</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Educação</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>Educação</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>Educação, nível não especificado</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Ensino primário</t>
   </si>
   <si>
+    <t>Ensino básico</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>Ensino básico</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Segundo ciclo do ensino secundário (modificado e inclui dados do 11322)</t>
   </si>
   <si>
+    <t>Ensino secundário</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>Ensino secundário</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -148,12 +148,12 @@
     <t>Ensino superior</t>
   </si>
   <si>
+    <t>Ensino pós-secundário</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>Ensino pós-secundário</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -166,18 +166,18 @@
     <t>Política e gestão administrativa da saúde</t>
   </si>
   <si>
+    <t>Saúde, geral</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Saúde</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>Saúde</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>Saúde, geral</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -202,12 +202,12 @@
     <t>Cuidados de saúde básica</t>
   </si>
   <si>
+    <t>Saúde básica</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Saúde básica</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -259,12 +259,12 @@
     <t>Controle de DNT, geral</t>
   </si>
   <si>
+    <t>Doenças não transmissíveis (DNT)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Doenças não transmissíveis (DNT)</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -301,12 +301,12 @@
     <t>Política e gestão administrativa da população</t>
   </si>
   <si>
+    <t>Políticas/programas populacionais e saúde reprodutiva</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Políticas/programas populacionais e saúde reprodutiva</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -337,12 +337,12 @@
     <t>Política e gestão administrativa do setor da água</t>
   </si>
   <si>
+    <t>Abastecimento de água e saneamento</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Abastecimento de água e saneamento</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -409,18 +409,18 @@
     <t>Política e gestão administrativa do setor público</t>
   </si>
   <si>
+    <t>Governo e sociedade civil, geral</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Governo e sociedade civil</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>Governo e sociedade civil</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>Governo e sociedade civil, geral</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -517,12 +517,12 @@
     <t>Gestão e reforma do sistema de segurança</t>
   </si>
   <si>
+    <t>Conflitos, paz e segurança</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Conflitos, paz e segurança</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -559,12 +559,12 @@
     <t>Proteção social</t>
   </si>
   <si>
+    <t>Outros serviços e infraestruturas sociais</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Outros serviços e infraestruturas sociais</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -631,12 +631,12 @@
     <t>Política e gestão administrativa dos transportes</t>
   </si>
   <si>
+    <t>Transportes e armazenamento</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transportes e armazenamento</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -679,12 +679,12 @@
     <t>Política e gestão administrativa das comunicações</t>
   </si>
   <si>
+    <t>Comunicações</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Comunicações</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -709,18 +709,18 @@
     <t>Política e gestão administrativa da energia</t>
   </si>
   <si>
+    <t>Política energética</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Energia</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>Energia</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>Política energética</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -745,12 +745,12 @@
     <t>Geração de energia, fontes renováveis ​​– várias tecnologias</t>
   </si>
   <si>
+    <t>Geração de energia, fontes renováveis</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Geração de energia, fontes renováveis</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -805,12 +805,12 @@
     <t>Geração de energia, fontes não renováveis, não especificadas</t>
   </si>
   <si>
+    <t>Geração de energia, fontes não renováveis</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Geração de energia, fontes não renováveis</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -847,36 +847,36 @@
     <t>Centrais de energia elétricas de energia híbrida</t>
   </si>
   <si>
+    <t>Centrais de energia híbridas</t>
+  </si>
+  <si>
     <t>234</t>
   </si>
   <si>
-    <t>Centrais de energia híbridas</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
     <t>Centrais de energia nucleares e segurança nuclear</t>
   </si>
   <si>
+    <t>Centrais de energia nuclear</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>Centrais de energia nuclear</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Centrais de aquecimento</t>
   </si>
   <si>
+    <t>Distribuição de energia</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Distribuição de energia</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -919,12 +919,12 @@
     <t>Política e gestão administrativa da área financeira</t>
   </si>
   <si>
+    <t>Serviços bancários e financeiros</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Serviços bancários e financeiros</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -961,12 +961,12 @@
     <t>Política e administração de negócios</t>
   </si>
   <si>
+    <t>Negócios e outros serviços</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Negócios e outros serviços</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -991,18 +991,18 @@
     <t>Política e gestão administrativa da agricultura</t>
   </si>
   <si>
+    <t>Agricultura</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agricultura, Silvicultura, Pesca</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>Agricultura, Silvicultura, Pesca</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Agricultura</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1111,12 +1111,12 @@
     <t>Política e gestão administrativa da silvicultura</t>
   </si>
   <si>
+    <t>Silvicultura</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>Silvicultura</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1153,12 +1153,12 @@
     <t>Política e gestão administrativa da pesca</t>
   </si>
   <si>
+    <t>Pesca</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>Pesca</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1189,18 +1189,18 @@
     <t>Política e gestão administrativa da indústria</t>
   </si>
   <si>
+    <t>Indústria</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Indústria, extractivas, construção</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>Indústria, extractivas, construção</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>Indústria</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1315,12 +1315,12 @@
     <t>Política e gestão administrativa dos minerais/minas</t>
   </si>
   <si>
+    <t>Recursos minerais e mineração</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>Recursos minerais e mineração</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1381,24 +1381,24 @@
     <t>Política e gestão administrativa da construção</t>
   </si>
   <si>
+    <t>Construção</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
-    <t>Construção</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
     <t>Política e gestão administrativa do comércio</t>
   </si>
   <si>
+    <t>Políticas comerciais e regulamentos</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Políticas comerciais e regulamentos</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1435,24 +1435,24 @@
     <t>Política e gestão administrativa do turismo</t>
   </si>
   <si>
+    <t>Turismo</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Turismo</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Política e gestão administrativa do ambiente</t>
   </si>
   <si>
+    <t>Proteção geral do ambiente</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>Proteção geral do ambiente</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1489,12 +1489,12 @@
     <t>Ajuda multissetorial</t>
   </si>
   <si>
+    <t>Outros, multissetoriais</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Outros, multissetoriais</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1555,36 +1555,36 @@
     <t>Ajuda relacionada com o apoio orçamental geral</t>
   </si>
   <si>
+    <t>Apoio orçamental geral</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>Apoio orçamental geral</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Assistência alimentar</t>
   </si>
   <si>
+    <t>Ajuda alimentar ao desenvolvimento</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Ajuda alimentar ao desenvolvimento</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Apoio à importação (bens de capital)</t>
   </si>
   <si>
+    <t>Outra ajuda por meio de mercadorias</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Outra ajuda por meio de mercadorias</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1642,12 +1642,12 @@
     <t>Assistência e serviços de alívio material</t>
   </si>
   <si>
+    <t>Resposta de emergência</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Resposta de emergência</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1666,58 +1666,58 @@
     <t>Reconstrução e reabilitação pós-emergência imediatas</t>
   </si>
   <si>
+    <t>Ajuda à reconstrução e reabilitação</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Ajuda à reconstrução e reabilitação</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Preparação da resposta contra vários riscos</t>
   </si>
   <si>
+    <t>Prevenção e preparação contra catástrofes</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Prevenção e preparação contra catástrofes</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Custos administrativos (não atribuíveis a setores)</t>
   </si>
   <si>
+    <t>Custos administrativos dos doadores</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Custos administrativos dos doadores</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugiados/requerentes de asilo em países doadores (não atribuíveis a setores)</t>
   </si>
   <si>
+    <t>Refugiados em países doadores</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugiados em países doadores</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Setores não especificados</t>
   </si>
   <si>
+    <t>Não atribuído/não especificado</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Não atribuído/não especificado</t>
   </si>
   <si>
     <t>99820</t>
@@ -7103,16 +7103,16 @@
         <v>9</v>
       </c>
       <c r="D220" t="s">
+        <v>526</v>
+      </c>
+      <c r="E220" t="s">
         <v>527</v>
       </c>
-      <c r="E220" t="s">
+      <c r="F220" t="s">
         <v>526</v>
       </c>
-      <c r="F220" t="s">
+      <c r="G220" t="s">
         <v>527</v>
-      </c>
-      <c r="G220" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7126,16 +7126,16 @@
         <v>9</v>
       </c>
       <c r="D221" t="s">
+        <v>526</v>
+      </c>
+      <c r="E221" t="s">
         <v>527</v>
       </c>
-      <c r="E221" t="s">
+      <c r="F221" t="s">
         <v>526</v>
       </c>
-      <c r="F221" t="s">
+      <c r="G221" t="s">
         <v>527</v>
-      </c>
-      <c r="G221" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7149,16 +7149,16 @@
         <v>9</v>
       </c>
       <c r="D222" t="s">
+        <v>526</v>
+      </c>
+      <c r="E222" t="s">
         <v>527</v>
       </c>
-      <c r="E222" t="s">
+      <c r="F222" t="s">
         <v>526</v>
       </c>
-      <c r="F222" t="s">
+      <c r="G222" t="s">
         <v>527</v>
-      </c>
-      <c r="G222" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7172,16 +7172,16 @@
         <v>9</v>
       </c>
       <c r="D223" t="s">
+        <v>526</v>
+      </c>
+      <c r="E223" t="s">
         <v>527</v>
       </c>
-      <c r="E223" t="s">
+      <c r="F223" t="s">
         <v>526</v>
       </c>
-      <c r="F223" t="s">
+      <c r="G223" t="s">
         <v>527</v>
-      </c>
-      <c r="G223" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7195,16 +7195,16 @@
         <v>9</v>
       </c>
       <c r="D224" t="s">
+        <v>526</v>
+      </c>
+      <c r="E224" t="s">
         <v>527</v>
       </c>
-      <c r="E224" t="s">
+      <c r="F224" t="s">
         <v>526</v>
       </c>
-      <c r="F224" t="s">
+      <c r="G224" t="s">
         <v>527</v>
-      </c>
-      <c r="G224" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7218,16 +7218,16 @@
         <v>9</v>
       </c>
       <c r="D225" t="s">
+        <v>526</v>
+      </c>
+      <c r="E225" t="s">
         <v>527</v>
       </c>
-      <c r="E225" t="s">
+      <c r="F225" t="s">
         <v>526</v>
       </c>
-      <c r="F225" t="s">
+      <c r="G225" t="s">
         <v>527</v>
-      </c>
-      <c r="G225" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7241,16 +7241,16 @@
         <v>9</v>
       </c>
       <c r="D226" t="s">
+        <v>526</v>
+      </c>
+      <c r="E226" t="s">
         <v>527</v>
       </c>
-      <c r="E226" t="s">
+      <c r="F226" t="s">
         <v>526</v>
       </c>
-      <c r="F226" t="s">
+      <c r="G226" t="s">
         <v>527</v>
-      </c>
-      <c r="G226" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="227" spans="1:7">

--- a/api/1/xlsx/pt/SectorGroup.xlsx
+++ b/api/1/xlsx/pt/SectorGroup.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:category-name</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>Educação, nível não especificado</t>
   </si>
   <si>
+    <t>Educação</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Educação</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -169,15 +169,15 @@
     <t>Saúde, geral</t>
   </si>
   <si>
+    <t>Saúde</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Saúde</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -412,15 +412,15 @@
     <t>Governo e sociedade civil, geral</t>
   </si>
   <si>
+    <t>Governo e sociedade civil</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Governo e sociedade civil</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -712,15 +712,15 @@
     <t>Política energética</t>
   </si>
   <si>
+    <t>Energia</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Energia</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -994,15 +994,15 @@
     <t>Agricultura</t>
   </si>
   <si>
+    <t>Agricultura, Silvicultura, Pesca</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agricultura, Silvicultura, Pesca</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1192,13 +1192,13 @@
     <t>Indústria</t>
   </si>
   <si>
+    <t>Indústria, extractivas, construção</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>320</t>
-  </si>
-  <si>
-    <t>Indústria, extractivas, construção</t>
-  </si>
-  <si>
-    <t>321</t>
   </si>
   <si>
     <t>32120</t>
@@ -2190,10 +2190,10 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2213,10 +2213,10 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2236,10 +2236,10 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2259,10 +2259,10 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2282,10 +2282,10 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2305,10 +2305,10 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2328,10 +2328,10 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2351,10 +2351,10 @@
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2374,10 +2374,10 @@
         <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G14" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2397,10 +2397,10 @@
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="G15" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2420,10 +2420,10 @@
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="G16" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2535,10 +2535,10 @@
         <v>51</v>
       </c>
       <c r="F21" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G21" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2558,10 +2558,10 @@
         <v>51</v>
       </c>
       <c r="F22" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G22" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2581,10 +2581,10 @@
         <v>51</v>
       </c>
       <c r="F23" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G23" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2604,10 +2604,10 @@
         <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G24" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2627,10 +2627,10 @@
         <v>51</v>
       </c>
       <c r="F25" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G25" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2650,10 +2650,10 @@
         <v>51</v>
       </c>
       <c r="F26" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G26" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2673,10 +2673,10 @@
         <v>51</v>
       </c>
       <c r="F27" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G27" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2693,10 +2693,10 @@
         <v>51</v>
       </c>
       <c r="F28" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G28" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2716,10 +2716,10 @@
         <v>51</v>
       </c>
       <c r="F29" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G29" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2739,10 +2739,10 @@
         <v>51</v>
       </c>
       <c r="F30" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2762,10 +2762,10 @@
         <v>51</v>
       </c>
       <c r="F31" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="G31" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2785,10 +2785,10 @@
         <v>51</v>
       </c>
       <c r="F32" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="G32" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2808,10 +2808,10 @@
         <v>51</v>
       </c>
       <c r="F33" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="G33" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2831,10 +2831,10 @@
         <v>51</v>
       </c>
       <c r="F34" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="G34" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2854,10 +2854,10 @@
         <v>51</v>
       </c>
       <c r="F35" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="G35" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2874,10 +2874,10 @@
         <v>95</v>
       </c>
       <c r="E36" t="s">
+        <v>95</v>
+      </c>
+      <c r="F36" t="s">
         <v>96</v>
-      </c>
-      <c r="F36" t="s">
-        <v>95</v>
       </c>
       <c r="G36" t="s">
         <v>96</v>
@@ -2897,10 +2897,10 @@
         <v>95</v>
       </c>
       <c r="E37" t="s">
+        <v>95</v>
+      </c>
+      <c r="F37" t="s">
         <v>96</v>
-      </c>
-      <c r="F37" t="s">
-        <v>95</v>
       </c>
       <c r="G37" t="s">
         <v>96</v>
@@ -2920,10 +2920,10 @@
         <v>95</v>
       </c>
       <c r="E38" t="s">
+        <v>95</v>
+      </c>
+      <c r="F38" t="s">
         <v>96</v>
-      </c>
-      <c r="F38" t="s">
-        <v>95</v>
       </c>
       <c r="G38" t="s">
         <v>96</v>
@@ -2943,10 +2943,10 @@
         <v>95</v>
       </c>
       <c r="E39" t="s">
+        <v>95</v>
+      </c>
+      <c r="F39" t="s">
         <v>96</v>
-      </c>
-      <c r="F39" t="s">
-        <v>95</v>
       </c>
       <c r="G39" t="s">
         <v>96</v>
@@ -2966,10 +2966,10 @@
         <v>95</v>
       </c>
       <c r="E40" t="s">
+        <v>95</v>
+      </c>
+      <c r="F40" t="s">
         <v>96</v>
-      </c>
-      <c r="F40" t="s">
-        <v>95</v>
       </c>
       <c r="G40" t="s">
         <v>96</v>
@@ -2989,10 +2989,10 @@
         <v>107</v>
       </c>
       <c r="E41" t="s">
+        <v>107</v>
+      </c>
+      <c r="F41" t="s">
         <v>108</v>
-      </c>
-      <c r="F41" t="s">
-        <v>107</v>
       </c>
       <c r="G41" t="s">
         <v>108</v>
@@ -3012,10 +3012,10 @@
         <v>107</v>
       </c>
       <c r="E42" t="s">
+        <v>107</v>
+      </c>
+      <c r="F42" t="s">
         <v>108</v>
-      </c>
-      <c r="F42" t="s">
-        <v>107</v>
       </c>
       <c r="G42" t="s">
         <v>108</v>
@@ -3035,10 +3035,10 @@
         <v>107</v>
       </c>
       <c r="E43" t="s">
+        <v>107</v>
+      </c>
+      <c r="F43" t="s">
         <v>108</v>
-      </c>
-      <c r="F43" t="s">
-        <v>107</v>
       </c>
       <c r="G43" t="s">
         <v>108</v>
@@ -3058,10 +3058,10 @@
         <v>107</v>
       </c>
       <c r="E44" t="s">
+        <v>107</v>
+      </c>
+      <c r="F44" t="s">
         <v>108</v>
-      </c>
-      <c r="F44" t="s">
-        <v>107</v>
       </c>
       <c r="G44" t="s">
         <v>108</v>
@@ -3081,10 +3081,10 @@
         <v>107</v>
       </c>
       <c r="E45" t="s">
+        <v>107</v>
+      </c>
+      <c r="F45" t="s">
         <v>108</v>
-      </c>
-      <c r="F45" t="s">
-        <v>107</v>
       </c>
       <c r="G45" t="s">
         <v>108</v>
@@ -3104,10 +3104,10 @@
         <v>107</v>
       </c>
       <c r="E46" t="s">
+        <v>107</v>
+      </c>
+      <c r="F46" t="s">
         <v>108</v>
-      </c>
-      <c r="F46" t="s">
-        <v>107</v>
       </c>
       <c r="G46" t="s">
         <v>108</v>
@@ -3127,10 +3127,10 @@
         <v>107</v>
       </c>
       <c r="E47" t="s">
+        <v>107</v>
+      </c>
+      <c r="F47" t="s">
         <v>108</v>
-      </c>
-      <c r="F47" t="s">
-        <v>107</v>
       </c>
       <c r="G47" t="s">
         <v>108</v>
@@ -3150,10 +3150,10 @@
         <v>107</v>
       </c>
       <c r="E48" t="s">
+        <v>107</v>
+      </c>
+      <c r="F48" t="s">
         <v>108</v>
-      </c>
-      <c r="F48" t="s">
-        <v>107</v>
       </c>
       <c r="G48" t="s">
         <v>108</v>
@@ -3173,10 +3173,10 @@
         <v>107</v>
       </c>
       <c r="E49" t="s">
+        <v>107</v>
+      </c>
+      <c r="F49" t="s">
         <v>108</v>
-      </c>
-      <c r="F49" t="s">
-        <v>107</v>
       </c>
       <c r="G49" t="s">
         <v>108</v>
@@ -3196,10 +3196,10 @@
         <v>107</v>
       </c>
       <c r="E50" t="s">
+        <v>107</v>
+      </c>
+      <c r="F50" t="s">
         <v>108</v>
-      </c>
-      <c r="F50" t="s">
-        <v>107</v>
       </c>
       <c r="G50" t="s">
         <v>108</v>
@@ -3219,10 +3219,10 @@
         <v>107</v>
       </c>
       <c r="E51" t="s">
+        <v>107</v>
+      </c>
+      <c r="F51" t="s">
         <v>108</v>
-      </c>
-      <c r="F51" t="s">
-        <v>107</v>
       </c>
       <c r="G51" t="s">
         <v>108</v>
@@ -3613,10 +3613,10 @@
         <v>132</v>
       </c>
       <c r="F68" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="G68" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3636,10 +3636,10 @@
         <v>132</v>
       </c>
       <c r="F69" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="G69" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3659,10 +3659,10 @@
         <v>132</v>
       </c>
       <c r="F70" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="G70" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3682,10 +3682,10 @@
         <v>132</v>
       </c>
       <c r="F71" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="G71" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3705,10 +3705,10 @@
         <v>132</v>
       </c>
       <c r="F72" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="G72" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3728,10 +3728,10 @@
         <v>132</v>
       </c>
       <c r="F73" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="G73" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3748,10 +3748,10 @@
         <v>181</v>
       </c>
       <c r="E74" t="s">
+        <v>181</v>
+      </c>
+      <c r="F74" t="s">
         <v>182</v>
-      </c>
-      <c r="F74" t="s">
-        <v>181</v>
       </c>
       <c r="G74" t="s">
         <v>182</v>
@@ -3771,10 +3771,10 @@
         <v>181</v>
       </c>
       <c r="E75" t="s">
+        <v>181</v>
+      </c>
+      <c r="F75" t="s">
         <v>182</v>
-      </c>
-      <c r="F75" t="s">
-        <v>181</v>
       </c>
       <c r="G75" t="s">
         <v>182</v>
@@ -3794,10 +3794,10 @@
         <v>181</v>
       </c>
       <c r="E76" t="s">
+        <v>181</v>
+      </c>
+      <c r="F76" t="s">
         <v>182</v>
-      </c>
-      <c r="F76" t="s">
-        <v>181</v>
       </c>
       <c r="G76" t="s">
         <v>182</v>
@@ -3817,10 +3817,10 @@
         <v>181</v>
       </c>
       <c r="E77" t="s">
+        <v>181</v>
+      </c>
+      <c r="F77" t="s">
         <v>182</v>
-      </c>
-      <c r="F77" t="s">
-        <v>181</v>
       </c>
       <c r="G77" t="s">
         <v>182</v>
@@ -3840,10 +3840,10 @@
         <v>181</v>
       </c>
       <c r="E78" t="s">
+        <v>181</v>
+      </c>
+      <c r="F78" t="s">
         <v>182</v>
-      </c>
-      <c r="F78" t="s">
-        <v>181</v>
       </c>
       <c r="G78" t="s">
         <v>182</v>
@@ -3863,10 +3863,10 @@
         <v>181</v>
       </c>
       <c r="E79" t="s">
+        <v>181</v>
+      </c>
+      <c r="F79" t="s">
         <v>182</v>
-      </c>
-      <c r="F79" t="s">
-        <v>181</v>
       </c>
       <c r="G79" t="s">
         <v>182</v>
@@ -3886,10 +3886,10 @@
         <v>181</v>
       </c>
       <c r="E80" t="s">
+        <v>181</v>
+      </c>
+      <c r="F80" t="s">
         <v>182</v>
-      </c>
-      <c r="F80" t="s">
-        <v>181</v>
       </c>
       <c r="G80" t="s">
         <v>182</v>
@@ -3909,10 +3909,10 @@
         <v>181</v>
       </c>
       <c r="E81" t="s">
+        <v>181</v>
+      </c>
+      <c r="F81" t="s">
         <v>182</v>
-      </c>
-      <c r="F81" t="s">
-        <v>181</v>
       </c>
       <c r="G81" t="s">
         <v>182</v>
@@ -3932,10 +3932,10 @@
         <v>181</v>
       </c>
       <c r="E82" t="s">
+        <v>181</v>
+      </c>
+      <c r="F82" t="s">
         <v>182</v>
-      </c>
-      <c r="F82" t="s">
-        <v>181</v>
       </c>
       <c r="G82" t="s">
         <v>182</v>
@@ -3955,10 +3955,10 @@
         <v>181</v>
       </c>
       <c r="E83" t="s">
+        <v>181</v>
+      </c>
+      <c r="F83" t="s">
         <v>182</v>
-      </c>
-      <c r="F83" t="s">
-        <v>181</v>
       </c>
       <c r="G83" t="s">
         <v>182</v>
@@ -3978,10 +3978,10 @@
         <v>181</v>
       </c>
       <c r="E84" t="s">
+        <v>181</v>
+      </c>
+      <c r="F84" t="s">
         <v>182</v>
-      </c>
-      <c r="F84" t="s">
-        <v>181</v>
       </c>
       <c r="G84" t="s">
         <v>182</v>
@@ -4001,10 +4001,10 @@
         <v>205</v>
       </c>
       <c r="E85" t="s">
+        <v>205</v>
+      </c>
+      <c r="F85" t="s">
         <v>206</v>
-      </c>
-      <c r="F85" t="s">
-        <v>205</v>
       </c>
       <c r="G85" t="s">
         <v>206</v>
@@ -4024,10 +4024,10 @@
         <v>205</v>
       </c>
       <c r="E86" t="s">
+        <v>205</v>
+      </c>
+      <c r="F86" t="s">
         <v>206</v>
-      </c>
-      <c r="F86" t="s">
-        <v>205</v>
       </c>
       <c r="G86" t="s">
         <v>206</v>
@@ -4047,10 +4047,10 @@
         <v>205</v>
       </c>
       <c r="E87" t="s">
+        <v>205</v>
+      </c>
+      <c r="F87" t="s">
         <v>206</v>
-      </c>
-      <c r="F87" t="s">
-        <v>205</v>
       </c>
       <c r="G87" t="s">
         <v>206</v>
@@ -4070,10 +4070,10 @@
         <v>205</v>
       </c>
       <c r="E88" t="s">
+        <v>205</v>
+      </c>
+      <c r="F88" t="s">
         <v>206</v>
-      </c>
-      <c r="F88" t="s">
-        <v>205</v>
       </c>
       <c r="G88" t="s">
         <v>206</v>
@@ -4093,10 +4093,10 @@
         <v>205</v>
       </c>
       <c r="E89" t="s">
+        <v>205</v>
+      </c>
+      <c r="F89" t="s">
         <v>206</v>
-      </c>
-      <c r="F89" t="s">
-        <v>205</v>
       </c>
       <c r="G89" t="s">
         <v>206</v>
@@ -4116,10 +4116,10 @@
         <v>205</v>
       </c>
       <c r="E90" t="s">
+        <v>205</v>
+      </c>
+      <c r="F90" t="s">
         <v>206</v>
-      </c>
-      <c r="F90" t="s">
-        <v>205</v>
       </c>
       <c r="G90" t="s">
         <v>206</v>
@@ -4139,10 +4139,10 @@
         <v>205</v>
       </c>
       <c r="E91" t="s">
+        <v>205</v>
+      </c>
+      <c r="F91" t="s">
         <v>206</v>
-      </c>
-      <c r="F91" t="s">
-        <v>205</v>
       </c>
       <c r="G91" t="s">
         <v>206</v>
@@ -4162,10 +4162,10 @@
         <v>221</v>
       </c>
       <c r="E92" t="s">
+        <v>221</v>
+      </c>
+      <c r="F92" t="s">
         <v>222</v>
-      </c>
-      <c r="F92" t="s">
-        <v>221</v>
       </c>
       <c r="G92" t="s">
         <v>222</v>
@@ -4185,10 +4185,10 @@
         <v>221</v>
       </c>
       <c r="E93" t="s">
+        <v>221</v>
+      </c>
+      <c r="F93" t="s">
         <v>222</v>
-      </c>
-      <c r="F93" t="s">
-        <v>221</v>
       </c>
       <c r="G93" t="s">
         <v>222</v>
@@ -4208,10 +4208,10 @@
         <v>221</v>
       </c>
       <c r="E94" t="s">
+        <v>221</v>
+      </c>
+      <c r="F94" t="s">
         <v>222</v>
-      </c>
-      <c r="F94" t="s">
-        <v>221</v>
       </c>
       <c r="G94" t="s">
         <v>222</v>
@@ -4231,10 +4231,10 @@
         <v>221</v>
       </c>
       <c r="E95" t="s">
+        <v>221</v>
+      </c>
+      <c r="F95" t="s">
         <v>222</v>
-      </c>
-      <c r="F95" t="s">
-        <v>221</v>
       </c>
       <c r="G95" t="s">
         <v>222</v>
@@ -4349,10 +4349,10 @@
         <v>232</v>
       </c>
       <c r="F100" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G100" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4372,10 +4372,10 @@
         <v>232</v>
       </c>
       <c r="F101" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G101" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4395,10 +4395,10 @@
         <v>232</v>
       </c>
       <c r="F102" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G102" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4418,10 +4418,10 @@
         <v>232</v>
       </c>
       <c r="F103" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G103" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4441,10 +4441,10 @@
         <v>232</v>
       </c>
       <c r="F104" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G104" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4464,10 +4464,10 @@
         <v>232</v>
       </c>
       <c r="F105" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G105" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4487,10 +4487,10 @@
         <v>232</v>
       </c>
       <c r="F106" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G106" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4510,10 +4510,10 @@
         <v>232</v>
       </c>
       <c r="F107" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G107" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4533,10 +4533,10 @@
         <v>232</v>
       </c>
       <c r="F108" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G108" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4556,10 +4556,10 @@
         <v>232</v>
       </c>
       <c r="F109" t="s">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="G109" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4579,10 +4579,10 @@
         <v>232</v>
       </c>
       <c r="F110" t="s">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="G110" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4602,10 +4602,10 @@
         <v>232</v>
       </c>
       <c r="F111" t="s">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="G111" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4625,10 +4625,10 @@
         <v>232</v>
       </c>
       <c r="F112" t="s">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="G112" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4648,10 +4648,10 @@
         <v>232</v>
       </c>
       <c r="F113" t="s">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="G113" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4671,10 +4671,10 @@
         <v>232</v>
       </c>
       <c r="F114" t="s">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="G114" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4694,10 +4694,10 @@
         <v>232</v>
       </c>
       <c r="F115" t="s">
-        <v>233</v>
+        <v>278</v>
       </c>
       <c r="G115" t="s">
-        <v>278</v>
+        <v>234</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4717,10 +4717,10 @@
         <v>232</v>
       </c>
       <c r="F116" t="s">
-        <v>233</v>
+        <v>282</v>
       </c>
       <c r="G116" t="s">
-        <v>282</v>
+        <v>234</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4740,10 +4740,10 @@
         <v>232</v>
       </c>
       <c r="F117" t="s">
-        <v>233</v>
+        <v>286</v>
       </c>
       <c r="G117" t="s">
-        <v>286</v>
+        <v>234</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4763,10 +4763,10 @@
         <v>232</v>
       </c>
       <c r="F118" t="s">
-        <v>233</v>
+        <v>286</v>
       </c>
       <c r="G118" t="s">
-        <v>286</v>
+        <v>234</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4786,10 +4786,10 @@
         <v>232</v>
       </c>
       <c r="F119" t="s">
-        <v>233</v>
+        <v>286</v>
       </c>
       <c r="G119" t="s">
-        <v>286</v>
+        <v>234</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4809,10 +4809,10 @@
         <v>232</v>
       </c>
       <c r="F120" t="s">
-        <v>233</v>
+        <v>286</v>
       </c>
       <c r="G120" t="s">
-        <v>286</v>
+        <v>234</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4832,10 +4832,10 @@
         <v>232</v>
       </c>
       <c r="F121" t="s">
-        <v>233</v>
+        <v>286</v>
       </c>
       <c r="G121" t="s">
-        <v>286</v>
+        <v>234</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4855,10 +4855,10 @@
         <v>232</v>
       </c>
       <c r="F122" t="s">
-        <v>233</v>
+        <v>286</v>
       </c>
       <c r="G122" t="s">
-        <v>286</v>
+        <v>234</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4878,10 +4878,10 @@
         <v>232</v>
       </c>
       <c r="F123" t="s">
-        <v>233</v>
+        <v>286</v>
       </c>
       <c r="G123" t="s">
-        <v>286</v>
+        <v>234</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4898,10 +4898,10 @@
         <v>301</v>
       </c>
       <c r="E124" t="s">
+        <v>301</v>
+      </c>
+      <c r="F124" t="s">
         <v>302</v>
-      </c>
-      <c r="F124" t="s">
-        <v>301</v>
       </c>
       <c r="G124" t="s">
         <v>302</v>
@@ -4921,10 +4921,10 @@
         <v>301</v>
       </c>
       <c r="E125" t="s">
+        <v>301</v>
+      </c>
+      <c r="F125" t="s">
         <v>302</v>
-      </c>
-      <c r="F125" t="s">
-        <v>301</v>
       </c>
       <c r="G125" t="s">
         <v>302</v>
@@ -4944,10 +4944,10 @@
         <v>301</v>
       </c>
       <c r="E126" t="s">
+        <v>301</v>
+      </c>
+      <c r="F126" t="s">
         <v>302</v>
-      </c>
-      <c r="F126" t="s">
-        <v>301</v>
       </c>
       <c r="G126" t="s">
         <v>302</v>
@@ -4967,10 +4967,10 @@
         <v>301</v>
       </c>
       <c r="E127" t="s">
+        <v>301</v>
+      </c>
+      <c r="F127" t="s">
         <v>302</v>
-      </c>
-      <c r="F127" t="s">
-        <v>301</v>
       </c>
       <c r="G127" t="s">
         <v>302</v>
@@ -4990,10 +4990,10 @@
         <v>301</v>
       </c>
       <c r="E128" t="s">
+        <v>301</v>
+      </c>
+      <c r="F128" t="s">
         <v>302</v>
-      </c>
-      <c r="F128" t="s">
-        <v>301</v>
       </c>
       <c r="G128" t="s">
         <v>302</v>
@@ -5013,10 +5013,10 @@
         <v>301</v>
       </c>
       <c r="E129" t="s">
+        <v>301</v>
+      </c>
+      <c r="F129" t="s">
         <v>302</v>
-      </c>
-      <c r="F129" t="s">
-        <v>301</v>
       </c>
       <c r="G129" t="s">
         <v>302</v>
@@ -5036,10 +5036,10 @@
         <v>315</v>
       </c>
       <c r="E130" t="s">
+        <v>315</v>
+      </c>
+      <c r="F130" t="s">
         <v>316</v>
-      </c>
-      <c r="F130" t="s">
-        <v>315</v>
       </c>
       <c r="G130" t="s">
         <v>316</v>
@@ -5059,10 +5059,10 @@
         <v>315</v>
       </c>
       <c r="E131" t="s">
+        <v>315</v>
+      </c>
+      <c r="F131" t="s">
         <v>316</v>
-      </c>
-      <c r="F131" t="s">
-        <v>315</v>
       </c>
       <c r="G131" t="s">
         <v>316</v>
@@ -5082,10 +5082,10 @@
         <v>315</v>
       </c>
       <c r="E132" t="s">
+        <v>315</v>
+      </c>
+      <c r="F132" t="s">
         <v>316</v>
-      </c>
-      <c r="F132" t="s">
-        <v>315</v>
       </c>
       <c r="G132" t="s">
         <v>316</v>
@@ -5105,10 +5105,10 @@
         <v>315</v>
       </c>
       <c r="E133" t="s">
+        <v>315</v>
+      </c>
+      <c r="F133" t="s">
         <v>316</v>
-      </c>
-      <c r="F133" t="s">
-        <v>315</v>
       </c>
       <c r="G133" t="s">
         <v>316</v>
@@ -5545,10 +5545,10 @@
         <v>326</v>
       </c>
       <c r="F152" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="G152" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5568,10 +5568,10 @@
         <v>326</v>
       </c>
       <c r="F153" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="G153" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5591,10 +5591,10 @@
         <v>326</v>
       </c>
       <c r="F154" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="G154" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5614,10 +5614,10 @@
         <v>326</v>
       </c>
       <c r="F155" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="G155" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5637,10 +5637,10 @@
         <v>326</v>
       </c>
       <c r="F156" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="G156" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5660,10 +5660,10 @@
         <v>326</v>
       </c>
       <c r="F157" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="G157" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5683,10 +5683,10 @@
         <v>326</v>
       </c>
       <c r="F158" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="G158" t="s">
-        <v>380</v>
+        <v>328</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5706,10 +5706,10 @@
         <v>326</v>
       </c>
       <c r="F159" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="G159" t="s">
-        <v>380</v>
+        <v>328</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5729,10 +5729,10 @@
         <v>326</v>
       </c>
       <c r="F160" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="G160" t="s">
-        <v>380</v>
+        <v>328</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5752,10 +5752,10 @@
         <v>326</v>
       </c>
       <c r="F161" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="G161" t="s">
-        <v>380</v>
+        <v>328</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5775,10 +5775,10 @@
         <v>326</v>
       </c>
       <c r="F162" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="G162" t="s">
-        <v>380</v>
+        <v>328</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -6235,10 +6235,10 @@
         <v>392</v>
       </c>
       <c r="F182" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G182" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6258,10 +6258,10 @@
         <v>392</v>
       </c>
       <c r="F183" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G183" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6281,10 +6281,10 @@
         <v>392</v>
       </c>
       <c r="F184" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G184" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6304,10 +6304,10 @@
         <v>392</v>
       </c>
       <c r="F185" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G185" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6327,10 +6327,10 @@
         <v>392</v>
       </c>
       <c r="F186" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G186" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6350,10 +6350,10 @@
         <v>392</v>
       </c>
       <c r="F187" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G187" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6373,10 +6373,10 @@
         <v>392</v>
       </c>
       <c r="F188" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G188" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6396,10 +6396,10 @@
         <v>392</v>
       </c>
       <c r="F189" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G189" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6419,10 +6419,10 @@
         <v>392</v>
       </c>
       <c r="F190" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G190" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6442,10 +6442,10 @@
         <v>392</v>
       </c>
       <c r="F191" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G191" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6465,10 +6465,10 @@
         <v>392</v>
       </c>
       <c r="F192" t="s">
-        <v>393</v>
+        <v>456</v>
       </c>
       <c r="G192" t="s">
-        <v>456</v>
+        <v>394</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6485,10 +6485,10 @@
         <v>459</v>
       </c>
       <c r="E193" t="s">
+        <v>459</v>
+      </c>
+      <c r="F193" t="s">
         <v>460</v>
-      </c>
-      <c r="F193" t="s">
-        <v>459</v>
       </c>
       <c r="G193" t="s">
         <v>460</v>
@@ -6508,10 +6508,10 @@
         <v>459</v>
       </c>
       <c r="E194" t="s">
+        <v>459</v>
+      </c>
+      <c r="F194" t="s">
         <v>460</v>
-      </c>
-      <c r="F194" t="s">
-        <v>459</v>
       </c>
       <c r="G194" t="s">
         <v>460</v>
@@ -6531,10 +6531,10 @@
         <v>459</v>
       </c>
       <c r="E195" t="s">
+        <v>459</v>
+      </c>
+      <c r="F195" t="s">
         <v>460</v>
-      </c>
-      <c r="F195" t="s">
-        <v>459</v>
       </c>
       <c r="G195" t="s">
         <v>460</v>
@@ -6554,10 +6554,10 @@
         <v>459</v>
       </c>
       <c r="E196" t="s">
+        <v>459</v>
+      </c>
+      <c r="F196" t="s">
         <v>460</v>
-      </c>
-      <c r="F196" t="s">
-        <v>459</v>
       </c>
       <c r="G196" t="s">
         <v>460</v>
@@ -6577,10 +6577,10 @@
         <v>459</v>
       </c>
       <c r="E197" t="s">
+        <v>459</v>
+      </c>
+      <c r="F197" t="s">
         <v>460</v>
-      </c>
-      <c r="F197" t="s">
-        <v>459</v>
       </c>
       <c r="G197" t="s">
         <v>460</v>
@@ -6600,10 +6600,10 @@
         <v>459</v>
       </c>
       <c r="E198" t="s">
+        <v>459</v>
+      </c>
+      <c r="F198" t="s">
         <v>460</v>
-      </c>
-      <c r="F198" t="s">
-        <v>459</v>
       </c>
       <c r="G198" t="s">
         <v>460</v>
@@ -6623,10 +6623,10 @@
         <v>473</v>
       </c>
       <c r="E199" t="s">
+        <v>473</v>
+      </c>
+      <c r="F199" t="s">
         <v>474</v>
-      </c>
-      <c r="F199" t="s">
-        <v>473</v>
       </c>
       <c r="G199" t="s">
         <v>474</v>
@@ -6646,10 +6646,10 @@
         <v>477</v>
       </c>
       <c r="E200" t="s">
+        <v>477</v>
+      </c>
+      <c r="F200" t="s">
         <v>478</v>
-      </c>
-      <c r="F200" t="s">
-        <v>477</v>
       </c>
       <c r="G200" t="s">
         <v>478</v>
@@ -6669,10 +6669,10 @@
         <v>477</v>
       </c>
       <c r="E201" t="s">
+        <v>477</v>
+      </c>
+      <c r="F201" t="s">
         <v>478</v>
-      </c>
-      <c r="F201" t="s">
-        <v>477</v>
       </c>
       <c r="G201" t="s">
         <v>478</v>
@@ -6692,10 +6692,10 @@
         <v>477</v>
       </c>
       <c r="E202" t="s">
+        <v>477</v>
+      </c>
+      <c r="F202" t="s">
         <v>478</v>
-      </c>
-      <c r="F202" t="s">
-        <v>477</v>
       </c>
       <c r="G202" t="s">
         <v>478</v>
@@ -6715,10 +6715,10 @@
         <v>477</v>
       </c>
       <c r="E203" t="s">
+        <v>477</v>
+      </c>
+      <c r="F203" t="s">
         <v>478</v>
-      </c>
-      <c r="F203" t="s">
-        <v>477</v>
       </c>
       <c r="G203" t="s">
         <v>478</v>
@@ -6738,10 +6738,10 @@
         <v>477</v>
       </c>
       <c r="E204" t="s">
+        <v>477</v>
+      </c>
+      <c r="F204" t="s">
         <v>478</v>
-      </c>
-      <c r="F204" t="s">
-        <v>477</v>
       </c>
       <c r="G204" t="s">
         <v>478</v>
@@ -6761,10 +6761,10 @@
         <v>477</v>
       </c>
       <c r="E205" t="s">
+        <v>477</v>
+      </c>
+      <c r="F205" t="s">
         <v>478</v>
-      </c>
-      <c r="F205" t="s">
-        <v>477</v>
       </c>
       <c r="G205" t="s">
         <v>478</v>
@@ -6784,10 +6784,10 @@
         <v>491</v>
       </c>
       <c r="E206" t="s">
+        <v>491</v>
+      </c>
+      <c r="F206" t="s">
         <v>492</v>
-      </c>
-      <c r="F206" t="s">
-        <v>491</v>
       </c>
       <c r="G206" t="s">
         <v>492</v>
@@ -6807,10 +6807,10 @@
         <v>491</v>
       </c>
       <c r="E207" t="s">
+        <v>491</v>
+      </c>
+      <c r="F207" t="s">
         <v>492</v>
-      </c>
-      <c r="F207" t="s">
-        <v>491</v>
       </c>
       <c r="G207" t="s">
         <v>492</v>
@@ -6830,10 +6830,10 @@
         <v>491</v>
       </c>
       <c r="E208" t="s">
+        <v>491</v>
+      </c>
+      <c r="F208" t="s">
         <v>492</v>
-      </c>
-      <c r="F208" t="s">
-        <v>491</v>
       </c>
       <c r="G208" t="s">
         <v>492</v>
@@ -6853,10 +6853,10 @@
         <v>491</v>
       </c>
       <c r="E209" t="s">
+        <v>491</v>
+      </c>
+      <c r="F209" t="s">
         <v>492</v>
-      </c>
-      <c r="F209" t="s">
-        <v>491</v>
       </c>
       <c r="G209" t="s">
         <v>492</v>
@@ -6876,10 +6876,10 @@
         <v>491</v>
       </c>
       <c r="E210" t="s">
+        <v>491</v>
+      </c>
+      <c r="F210" t="s">
         <v>492</v>
-      </c>
-      <c r="F210" t="s">
-        <v>491</v>
       </c>
       <c r="G210" t="s">
         <v>492</v>
@@ -6899,10 +6899,10 @@
         <v>491</v>
       </c>
       <c r="E211" t="s">
+        <v>491</v>
+      </c>
+      <c r="F211" t="s">
         <v>492</v>
-      </c>
-      <c r="F211" t="s">
-        <v>491</v>
       </c>
       <c r="G211" t="s">
         <v>492</v>
@@ -6922,10 +6922,10 @@
         <v>491</v>
       </c>
       <c r="E212" t="s">
+        <v>491</v>
+      </c>
+      <c r="F212" t="s">
         <v>492</v>
-      </c>
-      <c r="F212" t="s">
-        <v>491</v>
       </c>
       <c r="G212" t="s">
         <v>492</v>
@@ -6945,10 +6945,10 @@
         <v>491</v>
       </c>
       <c r="E213" t="s">
+        <v>491</v>
+      </c>
+      <c r="F213" t="s">
         <v>492</v>
-      </c>
-      <c r="F213" t="s">
-        <v>491</v>
       </c>
       <c r="G213" t="s">
         <v>492</v>
@@ -6968,10 +6968,10 @@
         <v>491</v>
       </c>
       <c r="E214" t="s">
+        <v>491</v>
+      </c>
+      <c r="F214" t="s">
         <v>492</v>
-      </c>
-      <c r="F214" t="s">
-        <v>491</v>
       </c>
       <c r="G214" t="s">
         <v>492</v>
@@ -6991,10 +6991,10 @@
         <v>491</v>
       </c>
       <c r="E215" t="s">
+        <v>491</v>
+      </c>
+      <c r="F215" t="s">
         <v>492</v>
-      </c>
-      <c r="F215" t="s">
-        <v>491</v>
       </c>
       <c r="G215" t="s">
         <v>492</v>
@@ -7014,10 +7014,10 @@
         <v>513</v>
       </c>
       <c r="E216" t="s">
+        <v>513</v>
+      </c>
+      <c r="F216" t="s">
         <v>514</v>
-      </c>
-      <c r="F216" t="s">
-        <v>513</v>
       </c>
       <c r="G216" t="s">
         <v>514</v>
@@ -7037,10 +7037,10 @@
         <v>517</v>
       </c>
       <c r="E217" t="s">
+        <v>517</v>
+      </c>
+      <c r="F217" t="s">
         <v>518</v>
-      </c>
-      <c r="F217" t="s">
-        <v>517</v>
       </c>
       <c r="G217" t="s">
         <v>518</v>
@@ -7060,10 +7060,10 @@
         <v>521</v>
       </c>
       <c r="E218" t="s">
+        <v>521</v>
+      </c>
+      <c r="F218" t="s">
         <v>522</v>
-      </c>
-      <c r="F218" t="s">
-        <v>521</v>
       </c>
       <c r="G218" t="s">
         <v>522</v>
@@ -7083,10 +7083,10 @@
         <v>521</v>
       </c>
       <c r="E219" t="s">
+        <v>521</v>
+      </c>
+      <c r="F219" t="s">
         <v>522</v>
-      </c>
-      <c r="F219" t="s">
-        <v>521</v>
       </c>
       <c r="G219" t="s">
         <v>522</v>
@@ -7106,10 +7106,10 @@
         <v>526</v>
       </c>
       <c r="E220" t="s">
+        <v>526</v>
+      </c>
+      <c r="F220" t="s">
         <v>527</v>
-      </c>
-      <c r="F220" t="s">
-        <v>526</v>
       </c>
       <c r="G220" t="s">
         <v>527</v>
@@ -7129,10 +7129,10 @@
         <v>526</v>
       </c>
       <c r="E221" t="s">
+        <v>526</v>
+      </c>
+      <c r="F221" t="s">
         <v>527</v>
-      </c>
-      <c r="F221" t="s">
-        <v>526</v>
       </c>
       <c r="G221" t="s">
         <v>527</v>
@@ -7152,10 +7152,10 @@
         <v>526</v>
       </c>
       <c r="E222" t="s">
+        <v>526</v>
+      </c>
+      <c r="F222" t="s">
         <v>527</v>
-      </c>
-      <c r="F222" t="s">
-        <v>526</v>
       </c>
       <c r="G222" t="s">
         <v>527</v>
@@ -7175,10 +7175,10 @@
         <v>526</v>
       </c>
       <c r="E223" t="s">
+        <v>526</v>
+      </c>
+      <c r="F223" t="s">
         <v>527</v>
-      </c>
-      <c r="F223" t="s">
-        <v>526</v>
       </c>
       <c r="G223" t="s">
         <v>527</v>
@@ -7198,10 +7198,10 @@
         <v>526</v>
       </c>
       <c r="E224" t="s">
+        <v>526</v>
+      </c>
+      <c r="F224" t="s">
         <v>527</v>
-      </c>
-      <c r="F224" t="s">
-        <v>526</v>
       </c>
       <c r="G224" t="s">
         <v>527</v>
@@ -7221,10 +7221,10 @@
         <v>526</v>
       </c>
       <c r="E225" t="s">
+        <v>526</v>
+      </c>
+      <c r="F225" t="s">
         <v>527</v>
-      </c>
-      <c r="F225" t="s">
-        <v>526</v>
       </c>
       <c r="G225" t="s">
         <v>527</v>
@@ -7244,10 +7244,10 @@
         <v>526</v>
       </c>
       <c r="E226" t="s">
+        <v>526</v>
+      </c>
+      <c r="F226" t="s">
         <v>527</v>
-      </c>
-      <c r="F226" t="s">
-        <v>526</v>
       </c>
       <c r="G226" t="s">
         <v>527</v>
@@ -7267,10 +7267,10 @@
         <v>542</v>
       </c>
       <c r="E227" t="s">
+        <v>542</v>
+      </c>
+      <c r="F227" t="s">
         <v>543</v>
-      </c>
-      <c r="F227" t="s">
-        <v>542</v>
       </c>
       <c r="G227" t="s">
         <v>543</v>
@@ -7290,10 +7290,10 @@
         <v>542</v>
       </c>
       <c r="E228" t="s">
+        <v>542</v>
+      </c>
+      <c r="F228" t="s">
         <v>543</v>
-      </c>
-      <c r="F228" t="s">
-        <v>542</v>
       </c>
       <c r="G228" t="s">
         <v>543</v>
@@ -7313,10 +7313,10 @@
         <v>542</v>
       </c>
       <c r="E229" t="s">
+        <v>542</v>
+      </c>
+      <c r="F229" t="s">
         <v>543</v>
-      </c>
-      <c r="F229" t="s">
-        <v>542</v>
       </c>
       <c r="G229" t="s">
         <v>543</v>
@@ -7336,10 +7336,10 @@
         <v>550</v>
       </c>
       <c r="E230" t="s">
+        <v>550</v>
+      </c>
+      <c r="F230" t="s">
         <v>551</v>
-      </c>
-      <c r="F230" t="s">
-        <v>550</v>
       </c>
       <c r="G230" t="s">
         <v>551</v>
@@ -7359,10 +7359,10 @@
         <v>554</v>
       </c>
       <c r="E231" t="s">
+        <v>554</v>
+      </c>
+      <c r="F231" t="s">
         <v>555</v>
-      </c>
-      <c r="F231" t="s">
-        <v>554</v>
       </c>
       <c r="G231" t="s">
         <v>555</v>
@@ -7382,10 +7382,10 @@
         <v>558</v>
       </c>
       <c r="E232" t="s">
+        <v>558</v>
+      </c>
+      <c r="F232" t="s">
         <v>559</v>
-      </c>
-      <c r="F232" t="s">
-        <v>558</v>
       </c>
       <c r="G232" t="s">
         <v>559</v>
@@ -7405,10 +7405,10 @@
         <v>562</v>
       </c>
       <c r="E233" t="s">
+        <v>562</v>
+      </c>
+      <c r="F233" t="s">
         <v>563</v>
-      </c>
-      <c r="F233" t="s">
-        <v>562</v>
       </c>
       <c r="G233" t="s">
         <v>563</v>
@@ -7428,10 +7428,10 @@
         <v>566</v>
       </c>
       <c r="E234" t="s">
+        <v>566</v>
+      </c>
+      <c r="F234" t="s">
         <v>567</v>
-      </c>
-      <c r="F234" t="s">
-        <v>566</v>
       </c>
       <c r="G234" t="s">
         <v>567</v>
@@ -7451,10 +7451,10 @@
         <v>566</v>
       </c>
       <c r="E235" t="s">
+        <v>566</v>
+      </c>
+      <c r="F235" t="s">
         <v>567</v>
-      </c>
-      <c r="F235" t="s">
-        <v>566</v>
       </c>
       <c r="G235" t="s">
         <v>567</v>
